--- a/Config/Datas/Recipes/Recipes.xlsx
+++ b/Config/Datas/Recipes/Recipes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\UnityProject\BBQ\Config\Datas\Recipes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\Recipes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97BC2508-4EAD-4203-945E-2ACFC0BA06AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE8F6AD-073A-4997-9BE8-7085AAC2C8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="25760" windowHeight="15440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,10 +75,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>list,GameAction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>规则描述</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -99,10 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RecipeRule_动态值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大餐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,10 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DV_值,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DV_值,6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -131,14 +119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*GA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GA_补充食材</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>actionDescription</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,10 +143,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GA_直接修改当前烧烤值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不饿不撑刚刚好！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,6 +152,50 @@
   </si>
   <si>
     <t>小巧精悍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>action</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*actions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition_DV检测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*conditions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -253,11 +273,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9" style="3"/>
@@ -548,12 +568,14 @@
     <col min="5" max="5" width="19.25" style="3" customWidth="1"/>
     <col min="6" max="6" width="19.5" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="22.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14.25" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="3"/>
+    <col min="8" max="8" width="4.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.25" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.25" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -570,21 +592,22 @@
         <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -603,152 +626,261 @@
       <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="8"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="3">
+      <c r="M5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="I7" s="1"/>
+      <c r="M7"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="3" t="s">
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G11" s="3">
+        <v>2</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G12" s="3">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B13" s="3">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G14" s="3">
+        <v>2</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="G15" s="3">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B9" s="3">
-        <v>2</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>33</v>
+      <c r="L15" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="H3:P3"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="G2:P2"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="M5:P5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Recipes/Recipes.xlsx
+++ b/Config/Datas/Recipes/Recipes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\Recipes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE8F6AD-073A-4997-9BE8-7085AAC2C8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7926F4-1870-4032-B045-C74A342856B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="25760" windowHeight="15440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="47">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -196,6 +196,22 @@
   </si>
   <si>
     <t>DV_值,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>优雅回文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回文串！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_回文串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DV_值,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -559,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9" style="3"/>
@@ -570,7 +586,7 @@
     <col min="7" max="7" width="18.875" style="3" customWidth="1"/>
     <col min="8" max="8" width="4.875" style="3" customWidth="1"/>
     <col min="9" max="9" width="18.875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="24.875" style="3" customWidth="1"/>
     <col min="11" max="11" width="14.25" style="3" customWidth="1"/>
     <col min="12" max="16384" width="9" style="3"/>
   </cols>
@@ -870,6 +886,66 @@
       </c>
       <c r="L15" s="3" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" x14ac:dyDescent="0.2">
+      <c r="G17" s="3">
+        <v>2</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" x14ac:dyDescent="0.2">
+      <c r="G18" s="3">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
